--- a/resources/births_hun.xlsx
+++ b/resources/births_hun.xlsx
@@ -8,29 +8,49 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CSURITA\PycharmProjects\PythonProject\counterfactual-analysis-vzv\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C4CC6A3-8B6B-4D53-A070-D8D98B3008D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{814BFC9F-87A5-432F-AC8E-AFAE6D404A05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="320" yWindow="1520" windowWidth="18880" windowHeight="8650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="320" yWindow="1900" windowWidth="18880" windowHeight="7080" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="births" sheetId="1" r:id="rId1"/>
+    <sheet name="weekly_data" sheetId="2" r:id="rId2"/>
+    <sheet name="weekly_rates" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
   <si>
     <t>Cases</t>
+  </si>
+  <si>
+    <t>week</t>
+  </si>
+  <si>
+    <t>2021–2025 mean</t>
+  </si>
+  <si>
+    <t>rates</t>
   </si>
 </sst>
 </file>
@@ -570,4 +590,1130 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBD6F20B-226B-42EF-93F6-1D8459A227E4}">
+  <dimension ref="A1:D53"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1">
+        <v>2026</v>
+      </c>
+      <c r="C1">
+        <v>2025</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1318</v>
+      </c>
+      <c r="C2">
+        <v>1411</v>
+      </c>
+      <c r="D2">
+        <v>1570</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1560</v>
+      </c>
+      <c r="C3">
+        <v>1457</v>
+      </c>
+      <c r="D3">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1443</v>
+      </c>
+      <c r="C4">
+        <v>1404</v>
+      </c>
+      <c r="D4">
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>1451</v>
+      </c>
+      <c r="C5">
+        <v>1458</v>
+      </c>
+      <c r="D5">
+        <v>1564</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>1332</v>
+      </c>
+      <c r="C6">
+        <v>1425</v>
+      </c>
+      <c r="D6">
+        <v>1582</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>1351</v>
+      </c>
+      <c r="C7">
+        <v>1395</v>
+      </c>
+      <c r="D7">
+        <v>1574</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>1308</v>
+      </c>
+      <c r="C8">
+        <v>1408</v>
+      </c>
+      <c r="D8">
+        <v>1564</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>1411</v>
+      </c>
+      <c r="C9">
+        <v>1434</v>
+      </c>
+      <c r="D9">
+        <v>1588</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>1309</v>
+      </c>
+      <c r="C10">
+        <v>1404</v>
+      </c>
+      <c r="D10">
+        <v>1587</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>1383</v>
+      </c>
+      <c r="C11">
+        <v>1374</v>
+      </c>
+      <c r="D11">
+        <v>1565</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>1329</v>
+      </c>
+      <c r="C12">
+        <v>1393</v>
+      </c>
+      <c r="D12">
+        <v>1519</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>1175</v>
+      </c>
+      <c r="C13">
+        <v>1320</v>
+      </c>
+      <c r="D13">
+        <v>1551</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="C14">
+        <v>1348</v>
+      </c>
+      <c r="D14">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="C15">
+        <v>1265</v>
+      </c>
+      <c r="D15">
+        <v>1433</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="C16">
+        <v>1185</v>
+      </c>
+      <c r="D16">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="C17">
+        <v>1242</v>
+      </c>
+      <c r="D17">
+        <v>1481</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="C18">
+        <v>1249</v>
+      </c>
+      <c r="D18">
+        <v>1517</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="C19">
+        <v>1204</v>
+      </c>
+      <c r="D19">
+        <v>1502</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="C20">
+        <v>1297</v>
+      </c>
+      <c r="D20">
+        <v>1543</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="C21">
+        <v>1309</v>
+      </c>
+      <c r="D21">
+        <v>1559</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="C22">
+        <v>1325</v>
+      </c>
+      <c r="D22">
+        <v>1519</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="C23">
+        <v>1367</v>
+      </c>
+      <c r="D23">
+        <v>1564</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="C24">
+        <v>1335</v>
+      </c>
+      <c r="D24">
+        <v>1569</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="C25">
+        <v>1303</v>
+      </c>
+      <c r="D25">
+        <v>1612</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="C26">
+        <v>1450</v>
+      </c>
+      <c r="D26">
+        <v>1707</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="C27">
+        <v>1477</v>
+      </c>
+      <c r="D27">
+        <v>1699</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="C28">
+        <v>1483</v>
+      </c>
+      <c r="D28">
+        <v>1698</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="C29">
+        <v>1492</v>
+      </c>
+      <c r="D29">
+        <v>1722</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="C30">
+        <v>1513</v>
+      </c>
+      <c r="D30">
+        <v>1733</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="C31">
+        <v>1533</v>
+      </c>
+      <c r="D31">
+        <v>1728</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="C32">
+        <v>1523</v>
+      </c>
+      <c r="D32">
+        <v>1715</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="C33">
+        <v>1525</v>
+      </c>
+      <c r="D33">
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="C34">
+        <v>1487</v>
+      </c>
+      <c r="D34">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="C35">
+        <v>1396</v>
+      </c>
+      <c r="D35">
+        <v>1656</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="C36">
+        <v>1422</v>
+      </c>
+      <c r="D36">
+        <v>1649</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="C37">
+        <v>1421</v>
+      </c>
+      <c r="D37">
+        <v>1689</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="C38">
+        <v>1402</v>
+      </c>
+      <c r="D38">
+        <v>1704</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="C39">
+        <v>1443</v>
+      </c>
+      <c r="D39">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="C40">
+        <v>1471</v>
+      </c>
+      <c r="D40">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="C41">
+        <v>1443</v>
+      </c>
+      <c r="D41">
+        <v>1654</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="C42">
+        <v>1317</v>
+      </c>
+      <c r="D42">
+        <v>1625</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="C43">
+        <v>1349</v>
+      </c>
+      <c r="D43">
+        <v>1572</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="C44">
+        <v>1274</v>
+      </c>
+      <c r="D44">
+        <v>1594</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="C45">
+        <v>1360</v>
+      </c>
+      <c r="D45">
+        <v>1565</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="C46">
+        <v>1348</v>
+      </c>
+      <c r="D46">
+        <v>1654</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="C47">
+        <v>1361</v>
+      </c>
+      <c r="D47">
+        <v>1557</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="C48">
+        <v>1300</v>
+      </c>
+      <c r="D48">
+        <v>1563</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="C49">
+        <v>1341</v>
+      </c>
+      <c r="D49">
+        <v>1557</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="C50">
+        <v>1416</v>
+      </c>
+      <c r="D50">
+        <v>1566</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="C51">
+        <v>1316</v>
+      </c>
+      <c r="D51">
+        <v>1529</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="C52">
+        <v>1369</v>
+      </c>
+      <c r="D52">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="C53">
+        <v>1196</v>
+      </c>
+      <c r="D53">
+        <v>1408</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E14FFDF-C307-4963-AEDC-9F2CA0F6F6E3}">
+  <dimension ref="A1:B54"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <f>weekly_data!D2/(SUM(weekly_data!D$2:D$53))</f>
+        <v>1.8914295352143218E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <f>weekly_data!D3/(SUM(weekly_data!D$2:D$53))</f>
+        <v>1.9275715008553598E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <f>weekly_data!D4/(SUM(weekly_data!D$2:D$53))</f>
+        <v>1.8793822133339758E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <f>weekly_data!D5/(SUM(weekly_data!D$2:D$53))</f>
+        <v>1.8842011420861143E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <f>weekly_data!D6/(SUM(weekly_data!D$2:D$53))</f>
+        <v>1.9058863214707372E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <f>weekly_data!D7/(SUM(weekly_data!D$2:D$53))</f>
+        <v>1.8962484639664604E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <f>weekly_data!D8/(SUM(weekly_data!D$2:D$53))</f>
+        <v>1.8842011420861143E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <f>weekly_data!D9/(SUM(weekly_data!D$2:D$53))</f>
+        <v>1.9131147145989447E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <f>weekly_data!D10/(SUM(weekly_data!D$2:D$53))</f>
+        <v>1.9119099824109101E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <f>weekly_data!D11/(SUM(weekly_data!D$2:D$53))</f>
+        <v>1.885405874274149E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <f>weekly_data!D12/(SUM(weekly_data!D$2:D$53))</f>
+        <v>1.8299881936245571E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <f>weekly_data!D13/(SUM(weekly_data!D$2:D$53))</f>
+        <v>1.8685396236416643E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <f>weekly_data!D14/(SUM(weekly_data!D$2:D$53))</f>
+        <v>1.8058935498638653E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <f>weekly_data!D15/(SUM(weekly_data!D$2:D$53))</f>
+        <v>1.7263812254535816E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <f>weekly_data!D16/(SUM(weekly_data!D$2:D$53))</f>
+        <v>1.7468616726501698E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <f>weekly_data!D17/(SUM(weekly_data!D$2:D$53))</f>
+        <v>1.7842083704792424E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <f>weekly_data!D18/(SUM(weekly_data!D$2:D$53))</f>
+        <v>1.8275787292484882E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <f>weekly_data!D19/(SUM(weekly_data!D$2:D$53))</f>
+        <v>1.8095077464279692E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <f>weekly_data!D20/(SUM(weekly_data!D$2:D$53))</f>
+        <v>1.8589017661373875E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <f>weekly_data!D21/(SUM(weekly_data!D$2:D$53))</f>
+        <v>1.8781774811459411E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <f>weekly_data!D22/(SUM(weekly_data!D$2:D$53))</f>
+        <v>1.8299881936245571E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <f>weekly_data!D23/(SUM(weekly_data!D$2:D$53))</f>
+        <v>1.8842011420861143E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <f>weekly_data!D24/(SUM(weekly_data!D$2:D$53))</f>
+        <v>1.8902248030262872E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <f>weekly_data!D25/(SUM(weekly_data!D$2:D$53))</f>
+        <v>1.9420282871117751E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <f>weekly_data!D26/(SUM(weekly_data!D$2:D$53))</f>
+        <v>2.0564778449750621E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <f>weekly_data!D27/(SUM(weekly_data!D$2:D$53))</f>
+        <v>2.0468399874707853E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <f>weekly_data!D28/(SUM(weekly_data!D$2:D$53))</f>
+        <v>2.0456352552827507E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <f>weekly_data!D29/(SUM(weekly_data!D$2:D$53))</f>
+        <v>2.0745488277955811E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <f>weekly_data!D30/(SUM(weekly_data!D$2:D$53))</f>
+        <v>2.0878008818639618E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <f>weekly_data!D31/(SUM(weekly_data!D$2:D$53))</f>
+        <v>2.0817772209237886E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <f>weekly_data!D32/(SUM(weekly_data!D$2:D$53))</f>
+        <v>2.0661157024793389E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <f>weekly_data!D33/(SUM(weekly_data!D$2:D$53))</f>
+        <v>2.0600920415391657E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <f>weekly_data!D34/(SUM(weekly_data!D$2:D$53))</f>
+        <v>2.0384068621545431E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <f>weekly_data!D35/(SUM(weekly_data!D$2:D$53))</f>
+        <v>1.9950365033852974E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <f>weekly_data!D36/(SUM(weekly_data!D$2:D$53))</f>
+        <v>1.9866033780690552E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <f>weekly_data!D37/(SUM(weekly_data!D$2:D$53))</f>
+        <v>2.0347926655904392E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <f>weekly_data!D38/(SUM(weekly_data!D$2:D$53))</f>
+        <v>2.0528636484109582E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <f>weekly_data!D39/(SUM(weekly_data!D$2:D$53))</f>
+        <v>2.0805724887357539E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <f>weekly_data!D40/(SUM(weekly_data!D$2:D$53))</f>
+        <v>2.0805724887357539E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <f>weekly_data!D41/(SUM(weekly_data!D$2:D$53))</f>
+        <v>1.9926270390092281E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <f>weekly_data!D42/(SUM(weekly_data!D$2:D$53))</f>
+        <v>1.9576898055562248E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43">
+        <f>weekly_data!D43/(SUM(weekly_data!D$2:D$53))</f>
+        <v>1.8938389995903911E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44">
+        <f>weekly_data!D44/(SUM(weekly_data!D$2:D$53))</f>
+        <v>1.9203431077271522E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45">
+        <f>weekly_data!D45/(SUM(weekly_data!D$2:D$53))</f>
+        <v>1.885405874274149E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46">
+        <f>weekly_data!D46/(SUM(weekly_data!D$2:D$53))</f>
+        <v>1.9926270390092281E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47">
+        <f>weekly_data!D47/(SUM(weekly_data!D$2:D$53))</f>
+        <v>1.8757680167698722E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48">
+        <f>weekly_data!D48/(SUM(weekly_data!D$2:D$53))</f>
+        <v>1.8829964098980797E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49">
+        <f>weekly_data!D49/(SUM(weekly_data!D$2:D$53))</f>
+        <v>1.8757680167698722E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50">
+        <f>weekly_data!D50/(SUM(weekly_data!D$2:D$53))</f>
+        <v>1.8866106064621836E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51">
+        <f>weekly_data!D51/(SUM(weekly_data!D$2:D$53))</f>
+        <v>1.8420355155049032E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52">
+        <f>weekly_data!D52/(SUM(weekly_data!D$2:D$53))</f>
+        <v>1.8480591764450764E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53">
+        <f>weekly_data!D53/(SUM(weekly_data!D$2:D$53))</f>
+        <v>1.6962629207527165E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>